--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -559,6 +569,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -626,6 +646,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -693,6 +723,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -760,6 +800,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -827,6 +877,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -894,6 +954,16 @@
           <t>150120</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -959,6 +1029,16 @@
           <t>150139</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1026,6 +1106,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1093,6 +1183,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1160,6 +1260,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1227,6 +1337,16 @@
           <t>150102</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1294,6 +1414,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1361,6 +1491,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1428,6 +1568,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1495,6 +1645,16 @@
           <t>150104</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1562,6 +1722,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1629,6 +1799,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1696,6 +1876,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1763,6 +1953,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1830,6 +2030,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1897,6 +2107,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1964,6 +2184,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2031,6 +2261,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2098,6 +2338,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2161,6 +2411,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2228,6 +2488,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2291,6 +2561,16 @@
           <t>010205</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2358,6 +2638,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2425,6 +2715,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2488,6 +2788,16 @@
           <t>010402</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE CENEPA</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2551,6 +2861,16 @@
           <t>010205</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2612,6 +2932,16 @@
           <t>010205</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2679,6 +3009,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2746,6 +3086,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2813,6 +3163,16 @@
           <t>150120</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2880,6 +3240,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2947,6 +3317,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3014,6 +3394,16 @@
           <t>150123</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3081,6 +3471,16 @@
           <t>150105</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3148,6 +3548,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3215,6 +3625,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3282,6 +3702,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3349,6 +3779,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3416,6 +3856,16 @@
           <t>150129</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3483,6 +3933,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3550,6 +4010,16 @@
           <t>150109</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3617,6 +4087,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3682,6 +4162,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3749,6 +4239,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3816,6 +4316,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3881,6 +4391,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3948,6 +4468,16 @@
           <t>150201</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4013,6 +4543,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4080,6 +4620,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4147,6 +4697,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4212,6 +4772,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4279,6 +4849,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4346,6 +4926,16 @@
           <t>150119</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4413,6 +5003,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4480,6 +5080,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4547,6 +5157,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4614,6 +5234,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4681,6 +5311,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4748,6 +5388,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4815,6 +5465,16 @@
           <t>150119</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4882,6 +5542,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4949,6 +5619,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5016,6 +5696,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5083,6 +5773,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5150,6 +5850,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5217,6 +5927,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5284,6 +6004,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5351,6 +6081,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5418,6 +6158,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5485,6 +6235,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5552,6 +6312,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5619,6 +6389,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5686,6 +6466,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5753,6 +6543,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5820,6 +6620,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5887,6 +6697,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5954,6 +6774,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6021,6 +6851,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6088,6 +6928,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6155,6 +7005,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6222,6 +7082,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6289,6 +7159,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6356,6 +7236,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6423,6 +7313,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6488,6 +7388,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6553,6 +7463,16 @@
           <t>200601</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>UGEL SULLANA</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6620,6 +7540,16 @@
           <t>150115</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6687,6 +7617,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6754,6 +7694,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6821,6 +7771,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6888,6 +7848,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6955,6 +7925,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7022,6 +8002,16 @@
           <t>150122</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7089,6 +8079,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7156,6 +8156,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7223,6 +8233,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7288,6 +8308,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7355,6 +8385,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7422,6 +8462,16 @@
           <t>010205</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7489,6 +8539,16 @@
           <t>010403</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7556,6 +8616,16 @@
           <t>010205</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>UGEL IBIR-IMAZA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7623,6 +8693,16 @@
           <t>010401</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>UGEL CONDORCANQUI</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7688,6 +8768,16 @@
           <t>081204</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7753,6 +8843,16 @@
           <t>090103</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAVELICA</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7818,6 +8918,16 @@
           <t>090206</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>DRE HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>UGEL ACOBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7883,6 +8993,16 @@
           <t>120907</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7950,6 +9070,16 @@
           <t>151028</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>UGEL 15 HUAROCHIRÍ</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8017,6 +9147,16 @@
           <t>081210</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8084,6 +9224,16 @@
           <t>210407</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8151,6 +9301,16 @@
           <t>210211</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8218,6 +9378,16 @@
           <t>210701</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>UGEL LAMPA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8285,6 +9455,16 @@
           <t>210504</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>UGEL EL COLLAO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8352,6 +9532,16 @@
           <t>211102</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>UGEL SAN ROMÁN</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8419,6 +9609,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8484,6 +9684,16 @@
           <t>250107</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>UGEL CORONEL PORTILLO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8549,6 +9759,16 @@
           <t>050510</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>UGEL LA MAR</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8616,6 +9836,16 @@
           <t>081204</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>UGEL QUISPICANCHI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8683,6 +9913,16 @@
           <t>210107</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>UGEL PUNO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8750,6 +9990,16 @@
           <t>210401</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8817,6 +10067,16 @@
           <t>210601</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8884,6 +10144,16 @@
           <t>210807</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>UGEL MELGAR</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8951,6 +10221,16 @@
           <t>080703</t>
         </is>
       </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9018,6 +10298,16 @@
           <t>080707</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>UGEL CHUMBIVILCAS</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9085,6 +10375,16 @@
           <t>210210</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9152,6 +10452,16 @@
           <t>210208</t>
         </is>
       </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9219,6 +10529,16 @@
           <t>210204</t>
         </is>
       </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9284,6 +10604,16 @@
           <t>210407</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9351,6 +10681,16 @@
           <t>081101</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>UGEL PAUCARTAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9418,6 +10758,16 @@
           <t>081104</t>
         </is>
       </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>UGEL PAUCARTAMBO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9483,6 +10833,16 @@
           <t>210403</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9546,6 +10906,16 @@
       <c r="O137" t="inlineStr">
         <is>
           <t>211003</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>UGEL SAN ANTONIO DE PUTINA</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q137"/>
+  <dimension ref="A1:R137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -579,6 +584,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -656,6 +666,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -733,6 +748,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -810,6 +830,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -887,6 +912,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -964,6 +994,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1039,6 +1074,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1116,6 +1156,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1193,6 +1238,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1270,6 +1320,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1347,6 +1402,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1424,6 +1484,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1501,6 +1566,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1578,6 +1648,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1655,6 +1730,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1732,6 +1812,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1809,6 +1894,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1886,6 +1976,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1963,6 +2058,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2040,6 +2140,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2117,6 +2222,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2194,6 +2304,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2271,6 +2386,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2348,6 +2468,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2421,6 +2546,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2498,6 +2628,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2571,6 +2706,11 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2648,6 +2788,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2725,6 +2870,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2798,6 +2948,11 @@
           <t>UGEL INTERCULTURAL BILINGE CENEPA</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2871,6 +3026,11 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2942,6 +3102,11 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3019,6 +3184,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3096,6 +3266,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3173,6 +3348,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3250,6 +3430,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3327,6 +3512,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3404,6 +3594,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3481,6 +3676,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3558,6 +3758,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3635,6 +3840,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3712,6 +3922,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3789,6 +4004,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3866,6 +4086,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3943,6 +4168,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4020,6 +4250,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4097,6 +4332,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4172,6 +4412,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4249,6 +4494,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4326,6 +4576,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4401,6 +4656,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4478,6 +4738,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4553,6 +4818,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4630,6 +4900,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4707,6 +4982,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4782,6 +5062,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4859,6 +5144,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4936,6 +5226,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5013,6 +5308,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5090,6 +5390,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5167,6 +5472,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5244,6 +5554,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5321,6 +5636,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5398,6 +5718,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5475,6 +5800,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5552,6 +5882,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5629,6 +5964,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5706,6 +6046,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5783,6 +6128,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5860,6 +6210,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5937,6 +6292,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6014,6 +6374,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6091,6 +6456,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6168,6 +6538,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6245,6 +6620,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6322,6 +6702,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6399,6 +6784,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6476,6 +6866,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6553,6 +6948,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6630,6 +7030,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6707,6 +7112,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6784,6 +7194,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6861,6 +7276,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6938,6 +7358,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7015,6 +7440,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7092,6 +7522,11 @@
           <t>DRE LIMA METROPOLITANA</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7169,6 +7604,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7246,6 +7686,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7323,6 +7768,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7398,6 +7848,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7473,6 +7928,11 @@
           <t>UGEL SULLANA</t>
         </is>
       </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7550,6 +8010,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7627,6 +8092,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7704,6 +8174,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7781,6 +8256,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7858,6 +8338,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7935,6 +8420,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8012,6 +8502,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8089,6 +8584,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8166,6 +8666,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8243,6 +8748,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8318,6 +8828,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8395,6 +8910,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8472,6 +8992,11 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8549,6 +9074,11 @@
           <t>UGEL INTERCULTURAL BILINGE RIO SANTIAGO</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8626,6 +9156,11 @@
           <t>UGEL IBIR-IMAZA</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8703,6 +9238,11 @@
           <t>UGEL CONDORCANQUI</t>
         </is>
       </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8778,6 +9318,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8853,6 +9398,11 @@
           <t>UGEL HUANCAVELICA</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8928,6 +9478,11 @@
           <t>UGEL ACOBAMBA</t>
         </is>
       </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -9003,6 +9558,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9080,6 +9640,11 @@
           <t>UGEL 15 HUAROCHIRÍ</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9157,6 +9722,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9234,6 +9804,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9311,6 +9886,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9388,6 +9968,11 @@
           <t>UGEL LAMPA</t>
         </is>
       </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9465,6 +10050,11 @@
           <t>UGEL EL COLLAO</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9542,6 +10132,11 @@
           <t>UGEL SAN ROMÁN</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9619,6 +10214,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9694,6 +10294,11 @@
           <t>UGEL CORONEL PORTILLO</t>
         </is>
       </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9769,6 +10374,11 @@
           <t>UGEL LA MAR</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9846,6 +10456,11 @@
           <t>UGEL QUISPICANCHI</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9923,6 +10538,11 @@
           <t>UGEL PUNO</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -10000,6 +10620,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -10077,6 +10702,11 @@
           <t>UGEL HUANCAN</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10154,6 +10784,11 @@
           <t>UGEL MELGAR</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10231,6 +10866,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10308,6 +10948,11 @@
           <t>UGEL CHUMBIVILCAS</t>
         </is>
       </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10385,6 +11030,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10462,6 +11112,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10539,6 +11194,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10614,6 +11274,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10691,6 +11356,11 @@
           <t>UGEL PAUCARTAMBO</t>
         </is>
       </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10768,6 +11438,11 @@
           <t>UGEL PAUCARTAMBO</t>
         </is>
       </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10843,6 +11518,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>UGM</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10916,6 +11596,11 @@
       <c r="Q137" t="inlineStr">
         <is>
           <t>UGEL SAN ANTONIO DE PUTINA</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>UGM</t>
         </is>
       </c>
     </row>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R137"/>
+  <dimension ref="A1:T137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,16 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -586,6 +596,16 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
+          <t>PEDRO ABRAHAM VALDELOMAR PINTO</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -668,6 +688,16 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>SEÑOR DE LOS MILAGROS II</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -750,6 +780,16 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>1243 SAN ROQUE</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -832,6 +872,16 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>6020 MICAELA BASTIDAS/6020 MICAELA BASTIDAS/6020 MICAELA BASTIDAS</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -914,6 +964,16 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
+          <t>1233 MANUEL FERNANDO CABREL NICHO/1233 MANUEL FERNANDO CABREL NICHO/1233 MANUEL FERNANDO CABREL NICHO</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -996,6 +1056,16 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
+          <t>095 MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1076,6 +1146,16 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1158,6 +1238,16 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>115-27 MI PEQUEÑO MUNDO</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1240,6 +1330,16 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>3082 PARAISO FLORIDO</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1322,6 +1422,16 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
+          <t>LAS BRISAS</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1404,6 +1514,16 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
+          <t>NUESTRA SEÑORA DE LA PAZ/NUESTRA SEÑORA DE LA PAZ/NUESTRA SEÑORA DE LA PAZ</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1486,6 +1606,16 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
+          <t>EL PORTILLO</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1568,6 +1698,16 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>ANTENOR ORREGO ESPINOZA/ANTENOR ORREGO ESPINOZA/ANTENOR ORREGO ESPINOZA/ANTENOR ORREGO ESPINOZA</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1650,6 +1790,16 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA/7064 MARIA AUXILIADORA</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1732,6 +1882,16 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
+          <t>7050 NICANOR RIVERA CACERES/7050 NICANOR RIVERA CACERES/7050 NICANOR RIVERA CACERES/7050 NICANOR RIVERA CACERES/7050 NICANOR RIVERA CACERES</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1814,6 +1974,16 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
+          <t>0367 VIRGEN DE LA MEDALLITA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1896,6 +2066,16 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
+          <t>1153 REPUBLICA DE CANADA/1153 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -1978,6 +2158,16 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
+          <t>1248 5 DE ABRIL/1248 5 DE ABRIL</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2060,6 +2250,16 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
+          <t>1254 MARIA REICHE NEWMANN/1254 MARIA REICHE NEWMANN/1254 MARIA REICHE NEWMANN</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2142,6 +2342,16 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
+          <t>3034 PAULO FREIRE</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2224,6 +2434,16 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
+          <t>7039 MANUEL SCORZA TORRES/7039 MANUEL SCORZA TORRES/7039 MANUEL SCORZA TORRES</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2306,6 +2526,16 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
+          <t>8190 SOL NACIENTE/8190 SOL NACIENTE</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2388,6 +2618,16 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
+          <t>CORONEL JOSE GALVEZ</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2470,6 +2710,16 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
+          <t>DULCE AMANECER</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2548,6 +2798,16 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
+          <t>MANUEL SEOANE CORRALES</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2630,6 +2890,16 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
+          <t>RICARDO BENTIN/RICARDO BENTIN/RICARDO BENTIN</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2708,6 +2978,16 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 55 VALENTIN SALEGUI</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2790,6 +3070,16 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
+          <t>WEEPIU YUU KUYU</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2872,6 +3162,16 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>YUMIGKUS</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -2950,6 +3250,16 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>DANIEL CHAMIKIT JUWAU</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3028,6 +3338,16 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 62 SAN JOSE/FE Y ALEGRIA 62 SAN JOSE/FE Y ALEGRIA 62 SAN JOSE</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3104,6 +3424,16 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
+          <t>16722</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3186,6 +3516,16 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
+          <t>2073 JOSE OLAYA BALANDRA/2073 JOSE OLAYA BALANDRA</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3268,6 +3608,16 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
+          <t>LOS ANGELITOS DE SAN JUAN</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3350,6 +3700,16 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
+          <t>012 REPUBLICA DOMINICANA</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3432,6 +3792,16 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
+          <t>6057 VIRGEN DE LOURDES/6057 VIRGEN DE LOURDES/6057 VIRGEN DE LOURDES</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3514,6 +3884,16 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
+          <t>JORGE LINGAN</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3596,6 +3976,16 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
+          <t>6100 SANTA MARIA REYNA/6100 SANTA MARIA REYNA</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3678,6 +4068,16 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
+          <t>BEATRIZ CISNEROS/BEATRIZ CISNEROS</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3760,6 +4160,16 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
+          <t>PADRE MIGUEL MARINA</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3842,6 +4252,16 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
+          <t>GOTITAS DE AMOR</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -3924,6 +4344,16 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
+          <t>SAN BARTOLOME/SAN BARTOLOME</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4006,6 +4436,16 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
+          <t>JESUSITO</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4088,6 +4528,16 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>6013 VIRGEN INMACULADA DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4170,6 +4620,16 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
+          <t>7106 VILLA LIMATAMBO/7106 VILLA LIMATAMBO</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4252,6 +4712,16 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
+          <t>6088/6088</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4334,6 +4804,16 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
+          <t>CASITA DEL SABER</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4414,6 +4894,16 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4496,6 +4986,16 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
+          <t>3024 JOSE ANTONIO ENCINAS/3024 JOSE ANTONIO ENCINAS/3024 JOSE ANTONIO ENCINAS</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4578,6 +5078,16 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
+          <t>3047 REPUBLICA DE CANADA/3047 REPUBLICA DE CANADA</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4658,6 +5168,16 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4740,6 +5260,16 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
+          <t>NIÑOS DEL FUTURO/NIÑOS DEL FUTURO</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4820,6 +5350,16 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4902,6 +5442,16 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
+          <t>VILLA DE LOURDES</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -4984,6 +5534,16 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
+          <t>0131 MONITOR HUASCAR/0131 MONITOR HUASCAR</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5064,6 +5624,16 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5146,6 +5716,16 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
+          <t>1178 JAVIER HERAUD/1178 JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5228,6 +5808,16 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
+          <t>665 SANTO DOMINGO DE HUARANGAL/665 SANTO DOMINGO DE HUARANGAL</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5310,6 +5900,16 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
+          <t>0061 LAS VIOLETAS</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5392,6 +5992,16 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
+          <t>018 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5474,6 +6084,16 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
+          <t>1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO/1173 JULIO CESAR TELLO</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5556,6 +6176,16 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
+          <t>7066 ANDRES AVELINO CACERES/7066 ANDRES AVELINO CACERES/7066 ANDRES AVELINO CACERES</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5638,6 +6268,16 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
+          <t>7075 JUAN PABLO II/7075 JUAN PABLO II/7075 JUAN PABLO II/7075 JUAN PABLO II/7075 JUAN PABLO II</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5720,6 +6360,16 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
+          <t>7079 RAMIRO PRIALE PRIALE/7079 RAMIRO PRIALE PRIALE</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5802,6 +6452,16 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
+          <t>LURIN</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5884,6 +6544,16 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
+          <t>LUIS NEGREIROS VEGA</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -5966,6 +6636,16 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
+          <t>SAN FRANCISCO DE ASIS</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6048,6 +6728,16 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
+          <t>VILLA MARIA</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6130,6 +6820,16 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
+          <t>2040 REPUBLICA DE CUBA/2040 REPUBLICA DE CUBA/2040 REPUBLICA DE CUBA</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6212,6 +6912,16 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
+          <t>LAS GARDENIAS</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6294,6 +7004,16 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
+          <t>LUCERITOS DE PACHACAMILLA</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6376,6 +7096,16 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
+          <t>2010 ALBERT EINSTEIN/2010 ALBERT EINSTEIN</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6458,6 +7188,16 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
+          <t>0342 MARIA Y JESUS</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6540,6 +7280,16 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
+          <t>SEÑOR DE LOS MILAGROS III</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6622,6 +7372,16 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
+          <t>391-1 FLOR DE AMANCAES</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6704,6 +7464,16 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
+          <t>0032 RAUL PORRAS BARRENECHEA/0032 RAUL PORRAS BARRENECHEA</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6786,6 +7556,16 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
+          <t>MI PEQUEÑO MUNDO III</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6868,6 +7648,16 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
+          <t>6047 JOSE MARIA ARGUEDAS/6047 JOSE MARIA ARGUEDAS/6047 JOSE MARIA ARGUEDAS/6047 JOSE MARIA ARGUEDAS</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -6950,6 +7740,16 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
+          <t>MEDALLA MILAGROSA/MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7032,6 +7832,16 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
+          <t>3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA/3037 GRAN AMAUTA</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7114,6 +7924,16 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
+          <t>7087 EL NAZARENO/7087 EL NAZARENO</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7196,6 +8016,16 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
+          <t>0015 LAS AZUCENAS</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7278,6 +8108,16 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
+          <t>1030 REPUBLICA DE BOLIVIA/1030 REPUBLICA DE BOLIVIA</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7360,6 +8200,16 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
+          <t>124 AUGUSTO SALAZAR BONDY</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7442,6 +8292,16 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
+          <t>7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA/7042 SANTA TERESA DE VILLA</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7524,6 +8384,16 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
+          <t>HUAYCAN</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7606,6 +8476,16 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
+          <t>LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7688,6 +8568,16 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
+          <t>103 LUIS ARMANDO CABELLO HURTADO/103 LUIS ARMANDO CABELLO HURTADO/103 LUIS ARMANDO CABELLO HURTADO</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7770,6 +8660,16 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
+          <t>GOTITAS DEL SABER</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7850,6 +8750,16 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -7930,6 +8840,16 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
+          <t>15027 AMAUTA/15027 AMAUTA/15027 AMAUTA</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8012,6 +8932,16 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
+          <t>020 MADRE TERESA DE CALCUTA/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO/020 MADRE TERESA DE CALCUTA/1120 PEDRO ADOLFO LABARTHE EFFIO/1120 PEDRO ADOLFO LABARTHE EFFIO</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8094,6 +9024,16 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
+          <t>1146 REPUBLICA DEL PARAGUAY/1146 REPUBLICA DEL PARAGUAY/1146 REPUBLICA DEL PARAGUAY</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8176,6 +9116,16 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
+          <t>1211 JOSE MARIA ARGUEDAS ALTAMIRANO/1211 JOSE MARIA ARGUEDAS ALTAMIRANO</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8258,6 +9208,16 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
+          <t>125 RICARDO PALMA/125 RICARDO PALMA</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8340,6 +9300,16 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
+          <t>3057/3057/3057 SANTA ROSA DE CARABAYLLO</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8422,6 +9392,16 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
+          <t>5172 HIJOS DE LUYA/5172 HIJOS DE LUYA</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8504,6 +9484,16 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
+          <t>FEDERICO VILLARREAL/FEDERICO VILLARREAL/FEDERICO VILLARREAL</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8586,6 +9576,16 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
+          <t>JOYITAS DE MARIA - I</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8668,6 +9668,16 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
+          <t>LOS PINOS/LOS PINOS</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8750,6 +9760,16 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
+          <t>TUPAC AMARU/TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8830,6 +9850,16 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8912,6 +9942,16 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
+          <t>517 MIS PEQUEÑITOS ANGELITOS</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -8994,6 +10034,16 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
+          <t>16714 SUWIKAI TSAKIM MIYAN/16714 SUWIKAI TSAKIM MIYAN</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9076,6 +10126,16 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
+          <t>RVDO. MANUEL GARCIA RENDUELES</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9158,6 +10218,16 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
+          <t>TEETS TSEJE</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9240,6 +10310,16 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
+          <t>CIRO ALEGRIA</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9320,6 +10400,16 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
+          <t>501335</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9400,6 +10490,16 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
+          <t>36315</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9480,6 +10580,16 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
+          <t>36749</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9560,6 +10670,16 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
+          <t>30089</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9642,6 +10762,16 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
+          <t>20733 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9724,6 +10854,16 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
+          <t>50546</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9806,6 +10946,16 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
+          <t>70301</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9888,6 +11038,16 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
+          <t>72044</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -9970,6 +11130,16 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10052,6 +11222,16 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10134,6 +11314,16 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
+          <t>939/70555</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10216,6 +11406,16 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10296,6 +11496,16 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10376,6 +11586,16 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
+          <t>38795</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10458,6 +11678,16 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
+          <t>1185/50557</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10540,6 +11770,16 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
+          <t>70068</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10622,6 +11862,16 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
+          <t>70213</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10704,6 +11954,16 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
+          <t>72262</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10786,6 +12046,16 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
+          <t>70500</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10868,6 +12138,16 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
+          <t>56341</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -10950,6 +12230,16 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
+          <t>56446</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11032,6 +12322,16 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11114,6 +12414,16 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
+          <t>72698</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11196,6 +12506,16 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
+          <t>661/72088</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11276,6 +12596,16 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
+          <t>70280</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11358,6 +12688,16 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
+          <t>240 CLORINDA MATTO DE TURNER</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11440,6 +12780,16 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
+          <t>50424/733/50424</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11520,6 +12870,16 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
           <t>UGM</t>
         </is>
       </c>
@@ -11599,6 +12959,16 @@
         </is>
       </c>
       <c r="R137" t="inlineStr">
+        <is>
+          <t>72135</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
         <is>
           <t>UGM</t>
         </is>

--- a/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
+++ b/output/bases_limpias/Grupo_04_ACONDICIONAMIENTO/df_ugm_acondicionamiento.xlsx
@@ -419,52 +419,52 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Año</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Local Escolar</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Tipo de intervención (mantenimiento correctivo, confort térmico o residencias estudiantiles)</t>
+          <t>tipo_de_intervencion_mantenimiento_correctivo_confort_termic</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Fecha estimada de entrega</t>
+          <t>fecha_estimada_de_entrega</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Monto contractual (S/)</t>
+          <t>monto_contractual</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Fase del proceso</t>
+          <t>fase_del_proceso</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Etapa del proceso</t>
+          <t>etapa_del_proceso</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Comentarios</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
